--- a/import_template_supplierinfo/tests/sample_error_missing_cols.xlsx
+++ b/import_template_supplierinfo/tests/sample_error_missing_cols.xlsx
@@ -25,7 +25,7 @@
     <t xml:space="preserve">column1</t>
   </si>
   <si>
-    <t xml:space="preserve">name</t>
+    <t xml:space="preserve">partner_id</t>
   </si>
   <si>
     <t xml:space="preserve">product_name</t>
@@ -166,23 +166,23 @@
     </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.89453125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.89"/>
@@ -190,8 +190,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.28"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="10" style="0" width="8.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
